--- a/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_13.xlsx
+++ b/Online Assessment 0/web_resources/Data files for Assessments/Online Assessment 0/Data3_13.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:C101"/>
+  <dimension ref="A1:C201"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -362,12 +362,12 @@
       </c>
       <c r="B1" s="1" t="inlineStr">
         <is>
-          <t>Group</t>
+          <t>IVOrd</t>
         </is>
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
-          <t>InformationLevel</t>
+          <t>Perfectionism</t>
         </is>
       </c>
     </row>
@@ -378,10 +378,10 @@
         </is>
       </c>
       <c r="B2">
-        <v>-0.1198132354319019</v>
+        <v>-0.2246644846475741</v>
       </c>
       <c r="C2">
-        <v>0.1399662064321995</v>
+        <v>-1.617923892874376</v>
       </c>
     </row>
     <row r="3">
@@ -391,10 +391,10 @@
         </is>
       </c>
       <c r="B3">
-        <v>0.7118056270480938</v>
+        <v>1.337816562421221</v>
       </c>
       <c r="C3">
-        <v>0.5194596568702556</v>
+        <v>0.1577009853118254</v>
       </c>
     </row>
     <row r="4">
@@ -404,10 +404,10 @@
         </is>
       </c>
       <c r="B4">
-        <v>-0.6051273162477022</v>
+        <v>-1.221512152693557</v>
       </c>
       <c r="C4">
-        <v>-1.405066084875723</v>
+        <v>0.8482145020190335</v>
       </c>
     </row>
     <row r="5">
@@ -417,10 +417,10 @@
         </is>
       </c>
       <c r="B5">
-        <v>1.704471012939563</v>
+        <v>-0.9206231392495265</v>
       </c>
       <c r="C5">
-        <v>1.157335569279438</v>
+        <v>-0.4859540805339549</v>
       </c>
     </row>
     <row r="6">
@@ -430,10 +430,10 @@
         </is>
       </c>
       <c r="B6">
-        <v>-2.748162377195527</v>
+        <v>-1.27641648239853</v>
       </c>
       <c r="C6">
-        <v>-0.7284310653839976</v>
+        <v>-0.8516365438026448</v>
       </c>
     </row>
     <row r="7">
@@ -443,10 +443,10 @@
         </is>
       </c>
       <c r="B7">
-        <v>-0.1391606361715583</v>
+        <v>-0.3680175710663109</v>
       </c>
       <c r="C7">
-        <v>0.3857899229993462</v>
+        <v>-0.341401456263436</v>
       </c>
     </row>
     <row r="8">
@@ -456,10 +456,10 @@
         </is>
       </c>
       <c r="B8">
-        <v>0.2700345139292182</v>
+        <v>0.9666697274701465</v>
       </c>
       <c r="C8">
-        <v>0.8013891493001974</v>
+        <v>1.907925626726025</v>
       </c>
     </row>
     <row r="9">
@@ -469,10 +469,10 @@
         </is>
       </c>
       <c r="B9">
-        <v>0.1552470896281456</v>
+        <v>-0.2173726523506171</v>
       </c>
       <c r="C9">
-        <v>0.663347011954708</v>
+        <v>-0.9474947331283681</v>
       </c>
     </row>
     <row r="10">
@@ -482,10 +482,10 @@
         </is>
       </c>
       <c r="B10">
-        <v>0.7129768352385424</v>
+        <v>0.5604452889480886</v>
       </c>
       <c r="C10">
-        <v>-0.2918139804315384</v>
+        <v>0.7641225509695581</v>
       </c>
     </row>
     <row r="11">
@@ -495,10 +495,10 @@
         </is>
       </c>
       <c r="B11">
-        <v>0.628763898578215</v>
+        <v>0.3634499215029629</v>
       </c>
       <c r="C11">
-        <v>0.8084997477647717</v>
+        <v>-0.4869067974377584</v>
       </c>
     </row>
     <row r="12">
@@ -508,10 +508,10 @@
         </is>
       </c>
       <c r="B12">
-        <v>-0.1158050770378273</v>
+        <v>-0.1237753680987692</v>
       </c>
       <c r="C12">
-        <v>-1.084278027415345</v>
+        <v>0.3018955016013274</v>
       </c>
     </row>
     <row r="13">
@@ -521,10 +521,10 @@
         </is>
       </c>
       <c r="B13">
-        <v>-0.4670428913239806</v>
+        <v>1.30821025690075</v>
       </c>
       <c r="C13">
-        <v>-0.797219273561679</v>
+        <v>1.188383795832767</v>
       </c>
     </row>
     <row r="14">
@@ -534,10 +534,10 @@
         </is>
       </c>
       <c r="B14">
-        <v>-0.2704992363563179</v>
+        <v>1.416908752092901</v>
       </c>
       <c r="C14">
-        <v>0.6259270098136397</v>
+        <v>1.813269401838327</v>
       </c>
     </row>
     <row r="15">
@@ -547,10 +547,10 @@
         </is>
       </c>
       <c r="B15">
-        <v>-0.9107021939383357</v>
+        <v>1.351201002229945</v>
       </c>
       <c r="C15">
-        <v>-1.209910866785955</v>
+        <v>0.3084314613354443</v>
       </c>
     </row>
     <row r="16">
@@ -560,10 +560,10 @@
         </is>
       </c>
       <c r="B16">
-        <v>1.087666359778788</v>
+        <v>-0.2972628409199176</v>
       </c>
       <c r="C16">
-        <v>1.122102353944789</v>
+        <v>-0.7799703693444697</v>
       </c>
     </row>
     <row r="17">
@@ -573,10 +573,10 @@
         </is>
       </c>
       <c r="B17">
-        <v>0.2347233250974354</v>
+        <v>-0.08627582445011246</v>
       </c>
       <c r="C17">
-        <v>0.1263571112426648</v>
+        <v>0.229551871767977</v>
       </c>
     </row>
     <row r="18">
@@ -586,10 +586,10 @@
         </is>
       </c>
       <c r="B18">
-        <v>0.3843127579827615</v>
+        <v>-0.8476165873993103</v>
       </c>
       <c r="C18">
-        <v>0.3333888172767918</v>
+        <v>1.356626136366729</v>
       </c>
     </row>
     <row r="19">
@@ -599,10 +599,10 @@
         </is>
       </c>
       <c r="B19">
-        <v>-1.041985118384634</v>
+        <v>-0.6413152452278352</v>
       </c>
       <c r="C19">
-        <v>-0.4759125349343974</v>
+        <v>-0.2461934815070769</v>
       </c>
     </row>
     <row r="20">
@@ -612,10 +612,10 @@
         </is>
       </c>
       <c r="B20">
-        <v>0.2480477839784759</v>
+        <v>0.1648644410475378</v>
       </c>
       <c r="C20">
-        <v>1.009032605310246</v>
+        <v>-1.938903252074105</v>
       </c>
     </row>
     <row r="21">
@@ -625,10 +625,10 @@
         </is>
       </c>
       <c r="B21">
-        <v>0.2780963663382894</v>
+        <v>-1.831314467493321</v>
       </c>
       <c r="C21">
-        <v>0.0374190862038382</v>
+        <v>1.039415919060287</v>
       </c>
     </row>
     <row r="22">
@@ -638,10 +638,10 @@
         </is>
       </c>
       <c r="B22">
-        <v>1.547940236237016</v>
+        <v>1.215712029830774</v>
       </c>
       <c r="C22">
-        <v>1.296983697030687</v>
+        <v>1.258978497109124</v>
       </c>
     </row>
     <row r="23">
@@ -651,10 +651,10 @@
         </is>
       </c>
       <c r="B23">
-        <v>0.2103141551498093</v>
+        <v>-0.2568864422223586</v>
       </c>
       <c r="C23">
-        <v>-0.7426592230060542</v>
+        <v>1.258225525187196</v>
       </c>
     </row>
     <row r="24">
@@ -664,10 +664,10 @@
         </is>
       </c>
       <c r="B24">
-        <v>-0.09220933977639753</v>
+        <v>-0.5376289987137379</v>
       </c>
       <c r="C24">
-        <v>-0.01066972012041507</v>
+        <v>1.272321693748813</v>
       </c>
     </row>
     <row r="25">
@@ -677,10 +677,10 @@
         </is>
       </c>
       <c r="B25">
-        <v>0.2590735246211919</v>
+        <v>-0.5826317266676709</v>
       </c>
       <c r="C25">
-        <v>1.05705599836669</v>
+        <v>1.261840168394618</v>
       </c>
     </row>
     <row r="26">
@@ -690,10 +690,10 @@
         </is>
       </c>
       <c r="B26">
-        <v>-1.169532905537274</v>
+        <v>0.5800305571752328</v>
       </c>
       <c r="C26">
-        <v>0.4534611759743011</v>
+        <v>-0.09263116062282942</v>
       </c>
     </row>
     <row r="27">
@@ -703,10 +703,10 @@
         </is>
       </c>
       <c r="B27">
-        <v>0.3231352025834544</v>
+        <v>0.8270869533409522</v>
       </c>
       <c r="C27">
-        <v>0.9098340696029905</v>
+        <v>0.4570163167222907</v>
       </c>
     </row>
     <row r="28">
@@ -716,10 +716,10 @@
         </is>
       </c>
       <c r="B28">
-        <v>0.7199859594188096</v>
+        <v>-0.5457667448236413</v>
       </c>
       <c r="C28">
-        <v>0.635320632860229</v>
+        <v>0.5959058111966736</v>
       </c>
     </row>
     <row r="29">
@@ -729,10 +729,10 @@
         </is>
       </c>
       <c r="B29">
-        <v>0.8958334376593622</v>
+        <v>0.5079471957048298</v>
       </c>
       <c r="C29">
-        <v>0.07503426840610239</v>
+        <v>0.03233795924702842</v>
       </c>
     </row>
     <row r="30">
@@ -742,10 +742,10 @@
         </is>
       </c>
       <c r="B30">
-        <v>0.4375767946446117</v>
+        <v>-1.799452674853214</v>
       </c>
       <c r="C30">
-        <v>0.7856442419675514</v>
+        <v>-0.6830126865214218</v>
       </c>
     </row>
     <row r="31">
@@ -755,10 +755,10 @@
         </is>
       </c>
       <c r="B31">
-        <v>-0.6841882455302173</v>
+        <v>0.6558388390222011</v>
       </c>
       <c r="C31">
-        <v>0.6662337306292</v>
+        <v>1.69537531531132</v>
       </c>
     </row>
     <row r="32">
@@ -768,10 +768,10 @@
         </is>
       </c>
       <c r="B32">
-        <v>1.22057736568207</v>
+        <v>-0.04234690695658993</v>
       </c>
       <c r="C32">
-        <v>-1.598602944846275</v>
+        <v>0.1998637670624814</v>
       </c>
     </row>
     <row r="33">
@@ -781,10 +781,10 @@
         </is>
       </c>
       <c r="B33">
-        <v>0.5394347304469611</v>
+        <v>-1.198862074949361</v>
       </c>
       <c r="C33">
-        <v>-0.03375168839357001</v>
+        <v>-0.6349676289663495</v>
       </c>
     </row>
     <row r="34">
@@ -794,10 +794,10 @@
         </is>
       </c>
       <c r="B34">
-        <v>0.3638450428571581</v>
+        <v>1.465097348321193</v>
       </c>
       <c r="C34">
-        <v>-0.3375477051793546</v>
+        <v>0.9220584577930067</v>
       </c>
     </row>
     <row r="35">
@@ -807,10 +807,10 @@
         </is>
       </c>
       <c r="B35">
-        <v>-0.584387918784544</v>
+        <v>-0.8666897466158477</v>
       </c>
       <c r="C35">
-        <v>0.1017846966907196</v>
+        <v>-1.009238138153782</v>
       </c>
     </row>
     <row r="36">
@@ -820,10 +820,10 @@
         </is>
       </c>
       <c r="B36">
-        <v>-1.637261533090274</v>
+        <v>-0.0948305346982259</v>
       </c>
       <c r="C36">
-        <v>-2.081937451821503</v>
+        <v>-1.037882447971559</v>
       </c>
     </row>
     <row r="37">
@@ -833,10 +833,10 @@
         </is>
       </c>
       <c r="B37">
-        <v>-1.005209772418153</v>
+        <v>-0.2507659523905209</v>
       </c>
       <c r="C37">
-        <v>0.6726711542154993</v>
+        <v>0.008435290929061048</v>
       </c>
     </row>
     <row r="38">
@@ -846,10 +846,10 @@
         </is>
       </c>
       <c r="B38">
-        <v>-0.9919347399160355</v>
+        <v>-0.04219236514341812</v>
       </c>
       <c r="C38">
-        <v>1.045238367002941</v>
+        <v>0.9141995810223045</v>
       </c>
     </row>
     <row r="39">
@@ -859,10 +859,10 @@
         </is>
       </c>
       <c r="B39">
-        <v>-0.05573942361486818</v>
+        <v>-0.6029973806169499</v>
       </c>
       <c r="C39">
-        <v>0.9604320009154046</v>
+        <v>-1.331315201977735</v>
       </c>
     </row>
     <row r="40">
@@ -872,10 +872,10 @@
         </is>
       </c>
       <c r="B40">
-        <v>-1.173893221270304</v>
+        <v>0.7381393469081501</v>
       </c>
       <c r="C40">
-        <v>-0.4517129216419634</v>
+        <v>-0.8424500685908843</v>
       </c>
     </row>
     <row r="41">
@@ -885,10 +885,10 @@
         </is>
       </c>
       <c r="B41">
-        <v>-0.07477799595906942</v>
+        <v>1.926424278741804</v>
       </c>
       <c r="C41">
-        <v>0.01522538284769788</v>
+        <v>0.8307697095716428</v>
       </c>
     </row>
     <row r="42">
@@ -898,10 +898,10 @@
         </is>
       </c>
       <c r="B42">
-        <v>1.150474518289585</v>
+        <v>-0.9358179343711421</v>
       </c>
       <c r="C42">
-        <v>-0.6199823917171938</v>
+        <v>0.5484388424088007</v>
       </c>
     </row>
     <row r="43">
@@ -911,10 +911,10 @@
         </is>
       </c>
       <c r="B43">
-        <v>-0.1630220260390585</v>
+        <v>0.913833138082549</v>
       </c>
       <c r="C43">
-        <v>-0.6499907151403466</v>
+        <v>0.2846261282245673</v>
       </c>
     </row>
     <row r="44">
@@ -924,10 +924,10 @@
         </is>
       </c>
       <c r="B44">
-        <v>-0.009861068602558929</v>
+        <v>-0.9145628994062918</v>
       </c>
       <c r="C44">
-        <v>-0.05379396598949833</v>
+        <v>0.05562450520090234</v>
       </c>
     </row>
     <row r="45">
@@ -937,10 +937,10 @@
         </is>
       </c>
       <c r="B45">
-        <v>0.6834340751677919</v>
+        <v>0.4850021965941033</v>
       </c>
       <c r="C45">
-        <v>-0.6971678267447023</v>
+        <v>-0.4053539650741345</v>
       </c>
     </row>
     <row r="46">
@@ -950,10 +950,10 @@
         </is>
       </c>
       <c r="B46">
-        <v>-0.68873868140427</v>
+        <v>0.02311194687170705</v>
       </c>
       <c r="C46">
-        <v>-0.2015666625185102</v>
+        <v>-0.1957046469375429</v>
       </c>
     </row>
     <row r="47">
@@ -963,10 +963,10 @@
         </is>
       </c>
       <c r="B47">
-        <v>0.8035592734831571</v>
+        <v>1.705618098763551</v>
       </c>
       <c r="C47">
-        <v>-0.2219996663361219</v>
+        <v>-0.5999517136706058</v>
       </c>
     </row>
     <row r="48">
@@ -976,10 +976,10 @@
         </is>
       </c>
       <c r="B48">
-        <v>1.093258047852322</v>
+        <v>-1.123746502670286</v>
       </c>
       <c r="C48">
-        <v>1.259527931438251</v>
+        <v>-1.911046879917848</v>
       </c>
     </row>
     <row r="49">
@@ -989,10 +989,10 @@
         </is>
       </c>
       <c r="B49">
-        <v>0.9484369473483925</v>
+        <v>-0.01566887892870527</v>
       </c>
       <c r="C49">
-        <v>0.9942714150877092</v>
+        <v>-0.2770931421465369</v>
       </c>
     </row>
     <row r="50">
@@ -1002,10 +1002,10 @@
         </is>
       </c>
       <c r="B50">
-        <v>-0.9622248006370272</v>
+        <v>-0.1030459663142478</v>
       </c>
       <c r="C50">
-        <v>-0.8162164691110939</v>
+        <v>-0.7832567196723366</v>
       </c>
     </row>
     <row r="51">
@@ -1015,10 +1015,10 @@
         </is>
       </c>
       <c r="B51">
-        <v>0.5462401352208398</v>
+        <v>-0.2117973349069966</v>
       </c>
       <c r="C51">
-        <v>0.528721500370735</v>
+        <v>-0.3368908694451633</v>
       </c>
     </row>
     <row r="52">
@@ -1028,10 +1028,10 @@
         </is>
       </c>
       <c r="B52">
-        <v>-0.0388329603467753</v>
+        <v>0.8447115389525692</v>
       </c>
       <c r="C52">
-        <v>1.391385106079049</v>
+        <v>0.4763348381609893</v>
       </c>
     </row>
     <row r="53">
@@ -1041,10 +1041,10 @@
         </is>
       </c>
       <c r="B53">
-        <v>-0.9163666338156665</v>
+        <v>-0.2895225987584042</v>
       </c>
       <c r="C53">
-        <v>-0.5310215166760686</v>
+        <v>0.2883878282307761</v>
       </c>
     </row>
     <row r="54">
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="B54">
-        <v>-0.2333787643893362</v>
+        <v>0.1840315952122851</v>
       </c>
       <c r="C54">
-        <v>-0.5925120184895056</v>
+        <v>1.852674178545981</v>
       </c>
     </row>
     <row r="55">
@@ -1067,10 +1067,10 @@
         </is>
       </c>
       <c r="B55">
-        <v>-0.9858656337762108</v>
+        <v>-0.1572729459074867</v>
       </c>
       <c r="C55">
-        <v>-0.1841215224965481</v>
+        <v>-0.2013152355954452</v>
       </c>
     </row>
     <row r="56">
@@ -1080,10 +1080,10 @@
         </is>
       </c>
       <c r="B56">
-        <v>-0.6273238597308457</v>
+        <v>-1.802776490876402</v>
       </c>
       <c r="C56">
-        <v>-2.323783781464151</v>
+        <v>-0.2056175944576717</v>
       </c>
     </row>
     <row r="57">
@@ -1093,10 +1093,10 @@
         </is>
       </c>
       <c r="B57">
-        <v>-0.3997326120152107</v>
+        <v>0.7827309021500893</v>
       </c>
       <c r="C57">
-        <v>-0.837612766580857</v>
+        <v>1.730054063937696</v>
       </c>
     </row>
     <row r="58">
@@ -1106,10 +1106,10 @@
         </is>
       </c>
       <c r="B58">
-        <v>0.7866687367067693</v>
+        <v>-0.1499815712438629</v>
       </c>
       <c r="C58">
-        <v>-1.376636965606343</v>
+        <v>-0.1903462542690114</v>
       </c>
     </row>
     <row r="59">
@@ -1119,10 +1119,10 @@
         </is>
       </c>
       <c r="B59">
-        <v>0.7967689490314787</v>
+        <v>0.2754139332244415</v>
       </c>
       <c r="C59">
-        <v>-1.254625681909099</v>
+        <v>-0.3527712325590838</v>
       </c>
     </row>
     <row r="60">
@@ -1132,10 +1132,10 @@
         </is>
       </c>
       <c r="B60">
-        <v>-0.5106119490794553</v>
+        <v>2.04598779689016</v>
       </c>
       <c r="C60">
-        <v>-0.589762204670377</v>
+        <v>-0.04914160258787914</v>
       </c>
     </row>
     <row r="61">
@@ -1145,10 +1145,10 @@
         </is>
       </c>
       <c r="B61">
-        <v>-0.1011508872666041</v>
+        <v>-0.1746956261173657</v>
       </c>
       <c r="C61">
-        <v>-0.9520177331828239</v>
+        <v>0.3635453920164771</v>
       </c>
     </row>
     <row r="62">
@@ -1158,10 +1158,10 @@
         </is>
       </c>
       <c r="B62">
-        <v>-0.386529539607768</v>
+        <v>0.05895533916045528</v>
       </c>
       <c r="C62">
-        <v>1.206810862160247</v>
+        <v>-0.2937580304368009</v>
       </c>
     </row>
     <row r="63">
@@ -1171,10 +1171,10 @@
         </is>
       </c>
       <c r="B63">
-        <v>1.309783945166012</v>
+        <v>-0.3952239694116749</v>
       </c>
       <c r="C63">
-        <v>1.270132372563412</v>
+        <v>-0.03081497923178619</v>
       </c>
     </row>
     <row r="64">
@@ -1184,10 +1184,10 @@
         </is>
       </c>
       <c r="B64">
-        <v>0.3622305574923551</v>
+        <v>-0.7528752260352399</v>
       </c>
       <c r="C64">
-        <v>0.572193274181945</v>
+        <v>-0.480354304361993</v>
       </c>
     </row>
     <row r="65">
@@ -1197,10 +1197,10 @@
         </is>
       </c>
       <c r="B65">
-        <v>-0.3943994890188005</v>
+        <v>0.3773265936976878</v>
       </c>
       <c r="C65">
-        <v>0.7227610311765373</v>
+        <v>-0.8047877448305456</v>
       </c>
     </row>
     <row r="66">
@@ -1210,10 +1210,10 @@
         </is>
       </c>
       <c r="B66">
-        <v>1.034174343959094</v>
+        <v>-0.06804475714354885</v>
       </c>
       <c r="C66">
-        <v>0.3713933199537368</v>
+        <v>0.3153210280777484</v>
       </c>
     </row>
     <row r="67">
@@ -1223,10 +1223,10 @@
         </is>
       </c>
       <c r="B67">
-        <v>0.8047110738865133</v>
+        <v>0.415606194301726</v>
       </c>
       <c r="C67">
-        <v>0.1480530214234299</v>
+        <v>0.7955850993965548</v>
       </c>
     </row>
     <row r="68">
@@ -1236,10 +1236,10 @@
         </is>
       </c>
       <c r="B68">
-        <v>0.9320639072391701</v>
+        <v>-0.03076984937331863</v>
       </c>
       <c r="C68">
-        <v>-0.445934582091889</v>
+        <v>0.02467456312129484</v>
       </c>
     </row>
     <row r="69">
@@ -1249,10 +1249,10 @@
         </is>
       </c>
       <c r="B69">
-        <v>0.960630180460371</v>
+        <v>-0.603253756288059</v>
       </c>
       <c r="C69">
-        <v>-0.1604187801603899</v>
+        <v>-0.3028740879858713</v>
       </c>
     </row>
     <row r="70">
@@ -1262,10 +1262,10 @@
         </is>
       </c>
       <c r="B70">
-        <v>-0.5721724495042889</v>
+        <v>-1.10854259231569</v>
       </c>
       <c r="C70">
-        <v>-0.3515820606073957</v>
+        <v>-1.336283142822082</v>
       </c>
     </row>
     <row r="71">
@@ -1275,10 +1275,10 @@
         </is>
       </c>
       <c r="B71">
-        <v>0.5199773314614917</v>
+        <v>0.2445526423167158</v>
       </c>
       <c r="C71">
-        <v>-0.4367320855764154</v>
+        <v>2.302652129576025</v>
       </c>
     </row>
     <row r="72">
@@ -1288,10 +1288,10 @@
         </is>
       </c>
       <c r="B72">
-        <v>0.568867778122103</v>
+        <v>-0.1118483008547359</v>
       </c>
       <c r="C72">
-        <v>1.179743178672273</v>
+        <v>-1.738014357313777</v>
       </c>
     </row>
     <row r="73">
@@ -1301,10 +1301,10 @@
         </is>
       </c>
       <c r="B73">
-        <v>-1.407839258884526</v>
+        <v>-0.7794229692344861</v>
       </c>
       <c r="C73">
-        <v>0.5019169605823701</v>
+        <v>-1.264259006485399</v>
       </c>
     </row>
     <row r="74">
@@ -1314,10 +1314,10 @@
         </is>
       </c>
       <c r="B74">
-        <v>0.1153477870578049</v>
+        <v>-0.50641107790456</v>
       </c>
       <c r="C74">
-        <v>1.6953810628421</v>
+        <v>-0.8675895066176852</v>
       </c>
     </row>
     <row r="75">
@@ -1327,10 +1327,10 @@
         </is>
       </c>
       <c r="B75">
-        <v>-0.5859889787617051</v>
+        <v>1.738884124297496</v>
       </c>
       <c r="C75">
-        <v>-1.185638102297363</v>
+        <v>-0.7318406908596662</v>
       </c>
     </row>
     <row r="76">
@@ -1340,10 +1340,10 @@
         </is>
       </c>
       <c r="B76">
-        <v>0.1451537676250868</v>
+        <v>-1.041186900422496</v>
       </c>
       <c r="C76">
-        <v>0.04250618593908494</v>
+        <v>1.056271653979916</v>
       </c>
     </row>
     <row r="77">
@@ -1353,10 +1353,10 @@
         </is>
       </c>
       <c r="B77">
-        <v>-1.773506986605386</v>
+        <v>-1.228960239406232</v>
       </c>
       <c r="C77">
-        <v>-2.389262178657593</v>
+        <v>0.4411444400076313</v>
       </c>
     </row>
     <row r="78">
@@ -1366,10 +1366,10 @@
         </is>
       </c>
       <c r="B78">
-        <v>0.4754629881844056</v>
+        <v>-1.040992815469941</v>
       </c>
       <c r="C78">
-        <v>0.8249554724507175</v>
+        <v>-0.155780837915616</v>
       </c>
     </row>
     <row r="79">
@@ -1379,10 +1379,10 @@
         </is>
       </c>
       <c r="B79">
-        <v>0.8937969814750006</v>
+        <v>0.1480384023615349</v>
       </c>
       <c r="C79">
-        <v>0.6391413901707612</v>
+        <v>0.2969985530293919</v>
       </c>
     </row>
     <row r="80">
@@ -1392,10 +1392,10 @@
         </is>
       </c>
       <c r="B80">
-        <v>1.284131001480659</v>
+        <v>-1.276338433720722</v>
       </c>
       <c r="C80">
-        <v>1.508784815908186</v>
+        <v>0.5883616209832944</v>
       </c>
     </row>
     <row r="81">
@@ -1405,10 +1405,10 @@
         </is>
       </c>
       <c r="B81">
-        <v>0.4697878614819667</v>
+        <v>-0.759843887376269</v>
       </c>
       <c r="C81">
-        <v>-0.6440317150203585</v>
+        <v>-1.294635467545006</v>
       </c>
     </row>
     <row r="82">
@@ -1418,10 +1418,10 @@
         </is>
       </c>
       <c r="B82">
-        <v>2.221765797299109</v>
+        <v>-1.057739248722737</v>
       </c>
       <c r="C82">
-        <v>-0.9109013785075015</v>
+        <v>-1.117221690004747</v>
       </c>
     </row>
     <row r="83">
@@ -1431,10 +1431,10 @@
         </is>
       </c>
       <c r="B83">
-        <v>-0.580824031143789</v>
+        <v>-0.7186915010945595</v>
       </c>
       <c r="C83">
-        <v>-0.5961289971334849</v>
+        <v>-0.3953404689953061</v>
       </c>
     </row>
     <row r="84">
@@ -1444,10 +1444,10 @@
         </is>
       </c>
       <c r="B84">
-        <v>0.1184799242092336</v>
+        <v>0.5230288201173436</v>
       </c>
       <c r="C84">
-        <v>-0.2693143076360995</v>
+        <v>1.736176067101189</v>
       </c>
     </row>
     <row r="85">
@@ -1457,10 +1457,10 @@
         </is>
       </c>
       <c r="B85">
-        <v>1.26004046247619</v>
+        <v>-0.4945993590297045</v>
       </c>
       <c r="C85">
-        <v>0.02625225885539789</v>
+        <v>-0.4811495426520997</v>
       </c>
     </row>
     <row r="86">
@@ -1470,10 +1470,10 @@
         </is>
       </c>
       <c r="B86">
-        <v>-2.313040838205883</v>
+        <v>0.9542460484207437</v>
       </c>
       <c r="C86">
-        <v>-3.099968165442021</v>
+        <v>-0.2905725539574895</v>
       </c>
     </row>
     <row r="87">
@@ -1483,10 +1483,10 @@
         </is>
       </c>
       <c r="B87">
-        <v>0.09007934595729766</v>
+        <v>-0.4814964428584761</v>
       </c>
       <c r="C87">
-        <v>0.03117772852579034</v>
+        <v>0.2940092217143265</v>
       </c>
     </row>
     <row r="88">
@@ -1496,10 +1496,10 @@
         </is>
       </c>
       <c r="B88">
-        <v>-0.2016861463923665</v>
+        <v>0.02798411216435056</v>
       </c>
       <c r="C88">
-        <v>1.501992040989509</v>
+        <v>-1.513303794082353</v>
       </c>
     </row>
     <row r="89">
@@ -1509,10 +1509,10 @@
         </is>
       </c>
       <c r="B89">
-        <v>1.785554452100268</v>
+        <v>1.42705709126878</v>
       </c>
       <c r="C89">
-        <v>1.741695256952937</v>
+        <v>0.4638077323033942</v>
       </c>
     </row>
     <row r="90">
@@ -1522,10 +1522,10 @@
         </is>
       </c>
       <c r="B90">
-        <v>0.06585136305047047</v>
+        <v>0.3927835112086993</v>
       </c>
       <c r="C90">
-        <v>-0.05773090863689907</v>
+        <v>-0.432550492561014</v>
       </c>
     </row>
     <row r="91">
@@ -1535,10 +1535,10 @@
         </is>
       </c>
       <c r="B91">
-        <v>-0.6449920588470414</v>
+        <v>-0.5999688904709014</v>
       </c>
       <c r="C91">
-        <v>-0.2660145032732441</v>
+        <v>1.342641029757284</v>
       </c>
     </row>
     <row r="92">
@@ -1548,10 +1548,10 @@
         </is>
       </c>
       <c r="B92">
-        <v>0.6990657442543079</v>
+        <v>0.3213036318418173</v>
       </c>
       <c r="C92">
-        <v>-0.4601024790944718</v>
+        <v>0.5806116554925584</v>
       </c>
     </row>
     <row r="93">
@@ -1561,10 +1561,10 @@
         </is>
       </c>
       <c r="B93">
-        <v>0.5341530533773741</v>
+        <v>0.01035517944664487</v>
       </c>
       <c r="C93">
-        <v>1.11139095444279</v>
+        <v>0.5863907509750333</v>
       </c>
     </row>
     <row r="94">
@@ -1574,10 +1574,10 @@
         </is>
       </c>
       <c r="B94">
-        <v>-0.8580493812719707</v>
+        <v>-0.1444751570647312</v>
       </c>
       <c r="C94">
-        <v>0.8392086956829503</v>
+        <v>0.3792083474892178</v>
       </c>
     </row>
     <row r="95">
@@ -1587,10 +1587,10 @@
         </is>
       </c>
       <c r="B95">
-        <v>-0.5546234320256406</v>
+        <v>-1.323833050408986</v>
       </c>
       <c r="C95">
-        <v>0.4326528580898442</v>
+        <v>-1.052243099838842</v>
       </c>
     </row>
     <row r="96">
@@ -1600,10 +1600,10 @@
         </is>
       </c>
       <c r="B96">
-        <v>0.2629316207479685</v>
+        <v>0.8841301556473914</v>
       </c>
       <c r="C96">
-        <v>-1.141369506680612</v>
+        <v>0.3465124865125994</v>
       </c>
     </row>
     <row r="97">
@@ -1613,10 +1613,10 @@
         </is>
       </c>
       <c r="B97">
-        <v>-0.3755311327744897</v>
+        <v>0.4292783332193421</v>
       </c>
       <c r="C97">
-        <v>-0.2514460102547237</v>
+        <v>-0.7338421980990946</v>
       </c>
     </row>
     <row r="98">
@@ -1626,10 +1626,10 @@
         </is>
       </c>
       <c r="B98">
-        <v>-0.1326757899380319</v>
+        <v>0.437113150191499</v>
       </c>
       <c r="C98">
-        <v>1.840428708927835</v>
+        <v>0.7346312325923827</v>
       </c>
     </row>
     <row r="99">
@@ -1639,10 +1639,10 @@
         </is>
       </c>
       <c r="B99">
-        <v>0.333078995007947</v>
+        <v>1.007929765936827</v>
       </c>
       <c r="C99">
-        <v>0.5050353117561557</v>
+        <v>0.01928467124894584</v>
       </c>
     </row>
     <row r="100">
@@ -1652,10 +1652,10 @@
         </is>
       </c>
       <c r="B100">
-        <v>0.2802137712464609</v>
+        <v>0.81762781355123</v>
       </c>
       <c r="C100">
-        <v>-0.5836037009721741</v>
+        <v>-1.543945672855012</v>
       </c>
     </row>
     <row r="101">
@@ -1665,10 +1665,1310 @@
         </is>
       </c>
       <c r="B101">
-        <v>-2.083853259729292</v>
+        <v>-0.1214769742371115</v>
       </c>
       <c r="C101">
-        <v>-1.268453025117644</v>
+        <v>1.404382430170498</v>
+      </c>
+    </row>
+    <row r="102">
+      <c r="A102" t="inlineStr">
+        <is>
+          <t>101</t>
+        </is>
+      </c>
+      <c r="B102">
+        <v>-0.5244427789543941</v>
+      </c>
+      <c r="C102">
+        <v>-0.3108245676565021</v>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" t="inlineStr">
+        <is>
+          <t>102</t>
+        </is>
+      </c>
+      <c r="B103">
+        <v>0.08833819113960452</v>
+      </c>
+      <c r="C103">
+        <v>-0.1896050315787587</v>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" t="inlineStr">
+        <is>
+          <t>103</t>
+        </is>
+      </c>
+      <c r="B104">
+        <v>-0.8922697136272114</v>
+      </c>
+      <c r="C104">
+        <v>0.7168095786657979</v>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" t="inlineStr">
+        <is>
+          <t>104</t>
+        </is>
+      </c>
+      <c r="B105">
+        <v>0.349624236720356</v>
+      </c>
+      <c r="C105">
+        <v>-0.1728323842120567</v>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" t="inlineStr">
+        <is>
+          <t>105</t>
+        </is>
+      </c>
+      <c r="B106">
+        <v>-0.4014054066657757</v>
+      </c>
+      <c r="C106">
+        <v>-1.343544262519217</v>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" t="inlineStr">
+        <is>
+          <t>106</t>
+        </is>
+      </c>
+      <c r="B107">
+        <v>1.232894572757583</v>
+      </c>
+      <c r="C107">
+        <v>0.5283681073123091</v>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" t="inlineStr">
+        <is>
+          <t>107</t>
+        </is>
+      </c>
+      <c r="B108">
+        <v>-1.114285602378857</v>
+      </c>
+      <c r="C108">
+        <v>0.8157949050755431</v>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" t="inlineStr">
+        <is>
+          <t>108</t>
+        </is>
+      </c>
+      <c r="B109">
+        <v>0.07706498397120479</v>
+      </c>
+      <c r="C109">
+        <v>-0.3435068190930135</v>
+      </c>
+    </row>
+    <row r="110">
+      <c r="A110" t="inlineStr">
+        <is>
+          <t>109</t>
+        </is>
+      </c>
+      <c r="B110">
+        <v>0.5028062887459532</v>
+      </c>
+      <c r="C110">
+        <v>-0.4937423056550028</v>
+      </c>
+    </row>
+    <row r="111">
+      <c r="A111" t="inlineStr">
+        <is>
+          <t>110</t>
+        </is>
+      </c>
+      <c r="B111">
+        <v>-0.8805873980175307</v>
+      </c>
+      <c r="C111">
+        <v>-1.094011486357683</v>
+      </c>
+    </row>
+    <row r="112">
+      <c r="A112" t="inlineStr">
+        <is>
+          <t>111</t>
+        </is>
+      </c>
+      <c r="B112">
+        <v>-0.2111739456495988</v>
+      </c>
+      <c r="C112">
+        <v>0.03571958479458139</v>
+      </c>
+    </row>
+    <row r="113">
+      <c r="A113" t="inlineStr">
+        <is>
+          <t>112</t>
+        </is>
+      </c>
+      <c r="B113">
+        <v>-0.2364087321218857</v>
+      </c>
+      <c r="C113">
+        <v>-0.517349539388873</v>
+      </c>
+    </row>
+    <row r="114">
+      <c r="A114" t="inlineStr">
+        <is>
+          <t>113</t>
+        </is>
+      </c>
+      <c r="B114">
+        <v>-0.9766978812901448</v>
+      </c>
+      <c r="C114">
+        <v>-0.06097645022820969</v>
+      </c>
+    </row>
+    <row r="115">
+      <c r="A115" t="inlineStr">
+        <is>
+          <t>114</t>
+        </is>
+      </c>
+      <c r="B115">
+        <v>0.3121248698012766</v>
+      </c>
+      <c r="C115">
+        <v>-1.02208482480173</v>
+      </c>
+    </row>
+    <row r="116">
+      <c r="A116" t="inlineStr">
+        <is>
+          <t>115</t>
+        </is>
+      </c>
+      <c r="B116">
+        <v>-0.2589639222728789</v>
+      </c>
+      <c r="C116">
+        <v>-0.1344547343169505</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" t="inlineStr">
+        <is>
+          <t>116</t>
+        </is>
+      </c>
+      <c r="B117">
+        <v>-1.017814782518678</v>
+      </c>
+      <c r="C117">
+        <v>-0.7643519956099609</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" t="inlineStr">
+        <is>
+          <t>117</t>
+        </is>
+      </c>
+      <c r="B118">
+        <v>1.361314331626802</v>
+      </c>
+      <c r="C118">
+        <v>0.1050058655032649</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" t="inlineStr">
+        <is>
+          <t>118</t>
+        </is>
+      </c>
+      <c r="B119">
+        <v>0.9232109680279529</v>
+      </c>
+      <c r="C119">
+        <v>2.187841045111995</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" t="inlineStr">
+        <is>
+          <t>119</t>
+        </is>
+      </c>
+      <c r="B120">
+        <v>0.3365627150264857</v>
+      </c>
+      <c r="C120">
+        <v>0.3311876762767403</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="B121">
+        <v>1.936331108128695</v>
+      </c>
+      <c r="C121">
+        <v>0.5970328959863398</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" t="inlineStr">
+        <is>
+          <t>121</t>
+        </is>
+      </c>
+      <c r="B122">
+        <v>-0.875872326244437</v>
+      </c>
+      <c r="C122">
+        <v>0.5745902516774057</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" t="inlineStr">
+        <is>
+          <t>122</t>
+        </is>
+      </c>
+      <c r="B123">
+        <v>1.150785610449429</v>
+      </c>
+      <c r="C123">
+        <v>1.686757167506576</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" t="inlineStr">
+        <is>
+          <t>123</t>
+        </is>
+      </c>
+      <c r="B124">
+        <v>-1.500284944300417</v>
+      </c>
+      <c r="C124">
+        <v>-0.5121111489157381</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" t="inlineStr">
+        <is>
+          <t>124</t>
+        </is>
+      </c>
+      <c r="B125">
+        <v>1.019279557785799</v>
+      </c>
+      <c r="C125">
+        <v>-0.3242853429002715</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" t="inlineStr">
+        <is>
+          <t>125</t>
+        </is>
+      </c>
+      <c r="B126">
+        <v>0.1805999067860614</v>
+      </c>
+      <c r="C126">
+        <v>-0.3592977894526415</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" t="inlineStr">
+        <is>
+          <t>126</t>
+        </is>
+      </c>
+      <c r="B127">
+        <v>-1.353880489076768</v>
+      </c>
+      <c r="C127">
+        <v>-1.498722959925867</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" t="inlineStr">
+        <is>
+          <t>127</t>
+        </is>
+      </c>
+      <c r="B128">
+        <v>-0.1454541156282651</v>
+      </c>
+      <c r="C128">
+        <v>-1.805500309952642</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" t="inlineStr">
+        <is>
+          <t>128</t>
+        </is>
+      </c>
+      <c r="B129">
+        <v>-2.126269721395145</v>
+      </c>
+      <c r="C129">
+        <v>-1.633737061319064</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" t="inlineStr">
+        <is>
+          <t>129</t>
+        </is>
+      </c>
+      <c r="B130">
+        <v>-0.6386032951466242</v>
+      </c>
+      <c r="C130">
+        <v>-0.448836826121816</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="B131">
+        <v>-0.8621920294007726</v>
+      </c>
+      <c r="C131">
+        <v>-1.477964214540746</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" t="inlineStr">
+        <is>
+          <t>131</t>
+        </is>
+      </c>
+      <c r="B132">
+        <v>-2.040785551231056</v>
+      </c>
+      <c r="C132">
+        <v>-1.166469974233074</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" t="inlineStr">
+        <is>
+          <t>132</t>
+        </is>
+      </c>
+      <c r="B133">
+        <v>-0.2884181157332173</v>
+      </c>
+      <c r="C133">
+        <v>0.3503756518157956</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" t="inlineStr">
+        <is>
+          <t>133</t>
+        </is>
+      </c>
+      <c r="B134">
+        <v>0.6908450201305784</v>
+      </c>
+      <c r="C134">
+        <v>0.6909830706553162</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" t="inlineStr">
+        <is>
+          <t>134</t>
+        </is>
+      </c>
+      <c r="B135">
+        <v>-0.2136169458376226</v>
+      </c>
+      <c r="C135">
+        <v>0.1544046140384981</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="B136">
+        <v>-1.606649349312208</v>
+      </c>
+      <c r="C136">
+        <v>-1.227328001400275</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" t="inlineStr">
+        <is>
+          <t>136</t>
+        </is>
+      </c>
+      <c r="B137">
+        <v>0.2725390210293319</v>
+      </c>
+      <c r="C137">
+        <v>-0.4190165963977068</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" t="inlineStr">
+        <is>
+          <t>137</t>
+        </is>
+      </c>
+      <c r="B138">
+        <v>-0.7191049254831811</v>
+      </c>
+      <c r="C138">
+        <v>-1.046130791187525</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" t="inlineStr">
+        <is>
+          <t>138</t>
+        </is>
+      </c>
+      <c r="B139">
+        <v>-1.068677153791186</v>
+      </c>
+      <c r="C139">
+        <v>0.1847989072107605</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" t="inlineStr">
+        <is>
+          <t>139</t>
+        </is>
+      </c>
+      <c r="B140">
+        <v>-0.122269725272143</v>
+      </c>
+      <c r="C140">
+        <v>0.07633749054280356</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="B141">
+        <v>0.2188880310182021</v>
+      </c>
+      <c r="C141">
+        <v>-0.3594649037612241</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="inlineStr">
+        <is>
+          <t>141</t>
+        </is>
+      </c>
+      <c r="B142">
+        <v>1.303058824713236</v>
+      </c>
+      <c r="C142">
+        <v>-0.4308658595194815</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="inlineStr">
+        <is>
+          <t>142</t>
+        </is>
+      </c>
+      <c r="B143">
+        <v>-0.5985037531740705</v>
+      </c>
+      <c r="C143">
+        <v>1.52449514289464</v>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="inlineStr">
+        <is>
+          <t>143</t>
+        </is>
+      </c>
+      <c r="B144">
+        <v>0.6385988875561563</v>
+      </c>
+      <c r="C144">
+        <v>1.601641275883561</v>
+      </c>
+    </row>
+    <row r="145">
+      <c r="A145" t="inlineStr">
+        <is>
+          <t>144</t>
+        </is>
+      </c>
+      <c r="B145">
+        <v>-1.449449799687987</v>
+      </c>
+      <c r="C145">
+        <v>-0.4357130181100173</v>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="B146">
+        <v>0.2045724694746029</v>
+      </c>
+      <c r="C146">
+        <v>-1.19986683748317</v>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" t="inlineStr">
+        <is>
+          <t>146</t>
+        </is>
+      </c>
+      <c r="B147">
+        <v>-0.1711580399390695</v>
+      </c>
+      <c r="C147">
+        <v>0.7109138255440729</v>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" t="inlineStr">
+        <is>
+          <t>147</t>
+        </is>
+      </c>
+      <c r="B148">
+        <v>-2.253633027726704</v>
+      </c>
+      <c r="C148">
+        <v>0.2227286651911488</v>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" t="inlineStr">
+        <is>
+          <t>148</t>
+        </is>
+      </c>
+      <c r="B149">
+        <v>-0.03835877051143614</v>
+      </c>
+      <c r="C149">
+        <v>1.475285512724168</v>
+      </c>
+    </row>
+    <row r="150">
+      <c r="A150" t="inlineStr">
+        <is>
+          <t>149</t>
+        </is>
+      </c>
+      <c r="B150">
+        <v>0.404666157415434</v>
+      </c>
+      <c r="C150">
+        <v>-0.8525534043113275</v>
+      </c>
+    </row>
+    <row r="151">
+      <c r="A151" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="B151">
+        <v>-0.1866402008653003</v>
+      </c>
+      <c r="C151">
+        <v>-0.3510701074212187</v>
+      </c>
+    </row>
+    <row r="152">
+      <c r="A152" t="inlineStr">
+        <is>
+          <t>151</t>
+        </is>
+      </c>
+      <c r="B152">
+        <v>-0.9319257706294922</v>
+      </c>
+      <c r="C152">
+        <v>0.3514337616782567</v>
+      </c>
+    </row>
+    <row r="153">
+      <c r="A153" t="inlineStr">
+        <is>
+          <t>152</t>
+        </is>
+      </c>
+      <c r="B153">
+        <v>0.5949681006211091</v>
+      </c>
+      <c r="C153">
+        <v>1.5479113897913</v>
+      </c>
+    </row>
+    <row r="154">
+      <c r="A154" t="inlineStr">
+        <is>
+          <t>153</t>
+        </is>
+      </c>
+      <c r="B154">
+        <v>0.2105786247121667</v>
+      </c>
+      <c r="C154">
+        <v>-0.4222032276803743</v>
+      </c>
+    </row>
+    <row r="155">
+      <c r="A155" t="inlineStr">
+        <is>
+          <t>154</t>
+        </is>
+      </c>
+      <c r="B155">
+        <v>0.465046828161917</v>
+      </c>
+      <c r="C155">
+        <v>1.957113687956761</v>
+      </c>
+    </row>
+    <row r="156">
+      <c r="A156" t="inlineStr">
+        <is>
+          <t>155</t>
+        </is>
+      </c>
+      <c r="B156">
+        <v>0.03051639055090297</v>
+      </c>
+      <c r="C156">
+        <v>-1.662765097197573</v>
+      </c>
+    </row>
+    <row r="157">
+      <c r="A157" t="inlineStr">
+        <is>
+          <t>156</t>
+        </is>
+      </c>
+      <c r="B157">
+        <v>-0.8462021200093116</v>
+      </c>
+      <c r="C157">
+        <v>-1.017872323631546</v>
+      </c>
+    </row>
+    <row r="158">
+      <c r="A158" t="inlineStr">
+        <is>
+          <t>157</t>
+        </is>
+      </c>
+      <c r="B158">
+        <v>-0.6000252115420798</v>
+      </c>
+      <c r="C158">
+        <v>-1.551126666735607</v>
+      </c>
+    </row>
+    <row r="159">
+      <c r="A159" t="inlineStr">
+        <is>
+          <t>158</t>
+        </is>
+      </c>
+      <c r="B159">
+        <v>0.1594837987536456</v>
+      </c>
+      <c r="C159">
+        <v>0.1390669543443321</v>
+      </c>
+    </row>
+    <row r="160">
+      <c r="A160" t="inlineStr">
+        <is>
+          <t>159</t>
+        </is>
+      </c>
+      <c r="B160">
+        <v>0.6217472024373243</v>
+      </c>
+      <c r="C160">
+        <v>0.8950555674371774</v>
+      </c>
+    </row>
+    <row r="161">
+      <c r="A161" t="inlineStr">
+        <is>
+          <t>160</t>
+        </is>
+      </c>
+      <c r="B161">
+        <v>-0.6330134549588426</v>
+      </c>
+      <c r="C161">
+        <v>-1.122776445081506</v>
+      </c>
+    </row>
+    <row r="162">
+      <c r="A162" t="inlineStr">
+        <is>
+          <t>161</t>
+        </is>
+      </c>
+      <c r="B162">
+        <v>0.6529814551436582</v>
+      </c>
+      <c r="C162">
+        <v>-1.033403756391997</v>
+      </c>
+    </row>
+    <row r="163">
+      <c r="A163" t="inlineStr">
+        <is>
+          <t>162</t>
+        </is>
+      </c>
+      <c r="B163">
+        <v>-0.9034392058556336</v>
+      </c>
+      <c r="C163">
+        <v>-1.870362369272859</v>
+      </c>
+    </row>
+    <row r="164">
+      <c r="A164" t="inlineStr">
+        <is>
+          <t>163</t>
+        </is>
+      </c>
+      <c r="B164">
+        <v>0.6327830890762982</v>
+      </c>
+      <c r="C164">
+        <v>0.3056127097204782</v>
+      </c>
+    </row>
+    <row r="165">
+      <c r="A165" t="inlineStr">
+        <is>
+          <t>164</t>
+        </is>
+      </c>
+      <c r="B165">
+        <v>-0.8649167028620823</v>
+      </c>
+      <c r="C165">
+        <v>0.5288178773819618</v>
+      </c>
+    </row>
+    <row r="166">
+      <c r="A166" t="inlineStr">
+        <is>
+          <t>165</t>
+        </is>
+      </c>
+      <c r="B166">
+        <v>0.3568359841722218</v>
+      </c>
+      <c r="C166">
+        <v>-0.4390461997474738</v>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="inlineStr">
+        <is>
+          <t>166</t>
+        </is>
+      </c>
+      <c r="B167">
+        <v>-0.6991346033274395</v>
+      </c>
+      <c r="C167">
+        <v>0.1717034669259843</v>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="inlineStr">
+        <is>
+          <t>167</t>
+        </is>
+      </c>
+      <c r="B168">
+        <v>-0.1976641541463768</v>
+      </c>
+      <c r="C168">
+        <v>1.803513825427418</v>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="inlineStr">
+        <is>
+          <t>168</t>
+        </is>
+      </c>
+      <c r="B169">
+        <v>0.9817703929756545</v>
+      </c>
+      <c r="C169">
+        <v>-1.10826611323925</v>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="inlineStr">
+        <is>
+          <t>169</t>
+        </is>
+      </c>
+      <c r="B170">
+        <v>1.651343212761045</v>
+      </c>
+      <c r="C170">
+        <v>1.308500003964375</v>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="inlineStr">
+        <is>
+          <t>170</t>
+        </is>
+      </c>
+      <c r="B171">
+        <v>0.8602437121062065</v>
+      </c>
+      <c r="C171">
+        <v>0.7990497402210482</v>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="inlineStr">
+        <is>
+          <t>171</t>
+        </is>
+      </c>
+      <c r="B172">
+        <v>2.217464698204606</v>
+      </c>
+      <c r="C172">
+        <v>1.458536688186195</v>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="B173">
+        <v>-0.9706306651287576</v>
+      </c>
+      <c r="C173">
+        <v>-0.05265076782834671</v>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="inlineStr">
+        <is>
+          <t>173</t>
+        </is>
+      </c>
+      <c r="B174">
+        <v>-0.2099758503738054</v>
+      </c>
+      <c r="C174">
+        <v>1.101873956289829</v>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="inlineStr">
+        <is>
+          <t>174</t>
+        </is>
+      </c>
+      <c r="B175">
+        <v>0.4092315189055623</v>
+      </c>
+      <c r="C175">
+        <v>0.2067437321850737</v>
+      </c>
+    </row>
+    <row r="176">
+      <c r="A176" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="B176">
+        <v>0.8136351672176924</v>
+      </c>
+      <c r="C176">
+        <v>0.07980451341909153</v>
+      </c>
+    </row>
+    <row r="177">
+      <c r="A177" t="inlineStr">
+        <is>
+          <t>176</t>
+        </is>
+      </c>
+      <c r="B177">
+        <v>1.082823920052396</v>
+      </c>
+      <c r="C177">
+        <v>-0.2415270498112104</v>
+      </c>
+    </row>
+    <row r="178">
+      <c r="A178" t="inlineStr">
+        <is>
+          <t>177</t>
+        </is>
+      </c>
+      <c r="B178">
+        <v>1.978204283534169</v>
+      </c>
+      <c r="C178">
+        <v>0.8519773914286106</v>
+      </c>
+    </row>
+    <row r="179">
+      <c r="A179" t="inlineStr">
+        <is>
+          <t>178</t>
+        </is>
+      </c>
+      <c r="B179">
+        <v>0.8281269766729281</v>
+      </c>
+      <c r="C179">
+        <v>1.541409951976172</v>
+      </c>
+    </row>
+    <row r="180">
+      <c r="A180" t="inlineStr">
+        <is>
+          <t>179</t>
+        </is>
+      </c>
+      <c r="B180">
+        <v>1.198993326914993</v>
+      </c>
+      <c r="C180">
+        <v>0.4874307895728824</v>
+      </c>
+    </row>
+    <row r="181">
+      <c r="A181" t="inlineStr">
+        <is>
+          <t>180</t>
+        </is>
+      </c>
+      <c r="B181">
+        <v>0.3951645390229043</v>
+      </c>
+      <c r="C181">
+        <v>0.4375736275047003</v>
+      </c>
+    </row>
+    <row r="182">
+      <c r="A182" t="inlineStr">
+        <is>
+          <t>181</t>
+        </is>
+      </c>
+      <c r="B182">
+        <v>-0.9602440634777445</v>
+      </c>
+      <c r="C182">
+        <v>-1.472347141641544</v>
+      </c>
+    </row>
+    <row r="183">
+      <c r="A183" t="inlineStr">
+        <is>
+          <t>182</t>
+        </is>
+      </c>
+      <c r="B183">
+        <v>-0.01772792620638882</v>
+      </c>
+      <c r="C183">
+        <v>-0.1510753077122374</v>
+      </c>
+    </row>
+    <row r="184">
+      <c r="A184" t="inlineStr">
+        <is>
+          <t>183</t>
+        </is>
+      </c>
+      <c r="B184">
+        <v>-0.6334745126608123</v>
+      </c>
+      <c r="C184">
+        <v>-1.742450543229518</v>
+      </c>
+    </row>
+    <row r="185">
+      <c r="A185" t="inlineStr">
+        <is>
+          <t>184</t>
+        </is>
+      </c>
+      <c r="B185">
+        <v>-0.1901034490085413</v>
+      </c>
+      <c r="C185">
+        <v>-0.4902796066377491</v>
+      </c>
+    </row>
+    <row r="186">
+      <c r="A186" t="inlineStr">
+        <is>
+          <t>185</t>
+        </is>
+      </c>
+      <c r="B186">
+        <v>0.6810311222631716</v>
+      </c>
+      <c r="C186">
+        <v>0.3372691131376054</v>
+      </c>
+    </row>
+    <row r="187">
+      <c r="A187" t="inlineStr">
+        <is>
+          <t>186</t>
+        </is>
+      </c>
+      <c r="B187">
+        <v>0.3971734917811145</v>
+      </c>
+      <c r="C187">
+        <v>0.1745473308926685</v>
+      </c>
+    </row>
+    <row r="188">
+      <c r="A188" t="inlineStr">
+        <is>
+          <t>187</t>
+        </is>
+      </c>
+      <c r="B188">
+        <v>-0.7346222992309914</v>
+      </c>
+      <c r="C188">
+        <v>-0.06925832511192945</v>
+      </c>
+    </row>
+    <row r="189">
+      <c r="A189" t="inlineStr">
+        <is>
+          <t>188</t>
+        </is>
+      </c>
+      <c r="B189">
+        <v>-0.6813603323268859</v>
+      </c>
+      <c r="C189">
+        <v>0.1569927996353993</v>
+      </c>
+    </row>
+    <row r="190">
+      <c r="A190" t="inlineStr">
+        <is>
+          <t>189</t>
+        </is>
+      </c>
+      <c r="B190">
+        <v>0.6281906251738583</v>
+      </c>
+      <c r="C190">
+        <v>1.198303212426202</v>
+      </c>
+    </row>
+    <row r="191">
+      <c r="A191" t="inlineStr">
+        <is>
+          <t>190</t>
+        </is>
+      </c>
+      <c r="B191">
+        <v>-1.102142897452088</v>
+      </c>
+      <c r="C191">
+        <v>0.008645705695991546</v>
+      </c>
+    </row>
+    <row r="192">
+      <c r="A192" t="inlineStr">
+        <is>
+          <t>191</t>
+        </is>
+      </c>
+      <c r="B192">
+        <v>0.1126101172278025</v>
+      </c>
+      <c r="C192">
+        <v>0.9861970295635281</v>
+      </c>
+    </row>
+    <row r="193">
+      <c r="A193" t="inlineStr">
+        <is>
+          <t>192</t>
+        </is>
+      </c>
+      <c r="B193">
+        <v>0.8748588599340912</v>
+      </c>
+      <c r="C193">
+        <v>0.4338239249550721</v>
+      </c>
+    </row>
+    <row r="194">
+      <c r="A194" t="inlineStr">
+        <is>
+          <t>193</t>
+        </is>
+      </c>
+      <c r="B194">
+        <v>1.602787822787292</v>
+      </c>
+      <c r="C194">
+        <v>0.7619304594341121</v>
+      </c>
+    </row>
+    <row r="195">
+      <c r="A195" t="inlineStr">
+        <is>
+          <t>194</t>
+        </is>
+      </c>
+      <c r="B195">
+        <v>0.72496579074034</v>
+      </c>
+      <c r="C195">
+        <v>1.091024628609549</v>
+      </c>
+    </row>
+    <row r="196">
+      <c r="A196" t="inlineStr">
+        <is>
+          <t>195</t>
+        </is>
+      </c>
+      <c r="B196">
+        <v>0.2139049095346154</v>
+      </c>
+      <c r="C196">
+        <v>-0.0321801720597064</v>
+      </c>
+    </row>
+    <row r="197">
+      <c r="A197" t="inlineStr">
+        <is>
+          <t>196</t>
+        </is>
+      </c>
+      <c r="B197">
+        <v>-1.1162698292339</v>
+      </c>
+      <c r="C197">
+        <v>-0.9524344723165533</v>
+      </c>
+    </row>
+    <row r="198">
+      <c r="A198" t="inlineStr">
+        <is>
+          <t>197</t>
+        </is>
+      </c>
+      <c r="B198">
+        <v>-0.3918298175097931</v>
+      </c>
+      <c r="C198">
+        <v>-1.996915498157848</v>
+      </c>
+    </row>
+    <row r="199">
+      <c r="A199" t="inlineStr">
+        <is>
+          <t>198</t>
+        </is>
+      </c>
+      <c r="B199">
+        <v>1.128075311874669</v>
+      </c>
+      <c r="C199">
+        <v>0.7710575166208349</v>
+      </c>
+    </row>
+    <row r="200">
+      <c r="A200" t="inlineStr">
+        <is>
+          <t>199</t>
+        </is>
+      </c>
+      <c r="B200">
+        <v>-0.2852383848099451</v>
+      </c>
+      <c r="C200">
+        <v>0.4652648076142441</v>
+      </c>
+    </row>
+    <row r="201">
+      <c r="A201" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="B201">
+        <v>-0.4825846037693928</v>
+      </c>
+      <c r="C201">
+        <v>-0.1504104226073756</v>
       </c>
     </row>
   </sheetData>
